--- a/docentes/González Altamirano Victorino Juventino - Estadisticos 20221.xlsx
+++ b/docentes/González Altamirano Victorino Juventino - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="73">
   <si>
     <t>Mat</t>
   </si>
@@ -100,33 +100,39 @@
     <t>TELE</t>
   </si>
   <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>MAY</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>APONTE</t>
+  </si>
+  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>APONTE</t>
-  </si>
-  <si>
     <t>VELASQUEZ</t>
   </si>
   <si>
@@ -142,30 +148,36 @@
     <t>HUERTA</t>
   </si>
   <si>
+    <t>ZEPACTLE</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>VIDERIQUE</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>PALACIOS</t>
+  </si>
+  <si>
+    <t>CHIMALHUA</t>
+  </si>
+  <si>
+    <t>OYOLA</t>
+  </si>
+  <si>
     <t>OJEDA</t>
   </si>
   <si>
-    <t>ZEPACTLE</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>CHIMALHUA</t>
-  </si>
-  <si>
-    <t>OYOLA</t>
-  </si>
-  <si>
     <t>VILLEGAS</t>
   </si>
   <si>
@@ -190,31 +202,37 @@
     <t>BETSABETH</t>
   </si>
   <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>GABRIELA AIMEE</t>
+  </si>
+  <si>
+    <t>BELEN</t>
+  </si>
+  <si>
+    <t>LESLY VIANEY</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>EMILIANO GERARDO</t>
+  </si>
+  <si>
+    <t>EVELYN ROSALIA</t>
+  </si>
+  <si>
+    <t>SALMA AISHA</t>
+  </si>
+  <si>
+    <t>IVON</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
     <t>ABIGAIL ANTONIA</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
-    <t>LESLY VIANEY</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>EMILIANO GERARDO</t>
-  </si>
-  <si>
-    <t>EVELYN ROSALIA</t>
-  </si>
-  <si>
-    <t>SALMA AISHA</t>
-  </si>
-  <si>
-    <t>IVON</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
   </si>
   <si>
     <t>IVETTE NAOMI</t>
@@ -722,10 +740,10 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F6">
         <v>24</v>
@@ -734,7 +752,7 @@
         <v>70.59</v>
       </c>
       <c r="H6">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -882,7 +900,7 @@
         <v>34</v>
       </c>
       <c r="E6">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1045,10 +1063,10 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F6">
         <v>24</v>
@@ -1057,7 +1075,7 @@
         <v>70.59</v>
       </c>
       <c r="H6">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -1067,7 +1085,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1105,10 +1123,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1128,10 +1146,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1151,10 +1169,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1174,10 +1192,10 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1197,10 +1215,10 @@
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1220,10 +1238,10 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1243,10 +1261,10 @@
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1260,16 +1278,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920130</v>
+        <v>22330051920131</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1283,16 +1301,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920131</v>
+        <v>22330051920136</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1306,22 +1324,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920155</v>
+        <v>22330051920141</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1329,16 +1347,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920386</v>
+        <v>22330051920155</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1352,39 +1370,39 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920205</v>
+        <v>22330051920386</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920222</v>
+        <v>22330051920205</v>
       </c>
       <c r="B14" t="s">
         <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1398,22 +1416,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920062</v>
+        <v>22330051920222</v>
       </c>
       <c r="B15" t="s">
         <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D15" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1421,22 +1439,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920119</v>
+        <v>22330051920062</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1444,22 +1462,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920125</v>
+        <v>22330051920119</v>
       </c>
       <c r="B17" t="s">
         <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1467,24 +1485,70 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
+        <v>22330051920125</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>22330051920130</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
         <v>22330051920269</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B20" t="s">
         <v>23</v>
       </c>
-      <c r="C18" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" t="s">
-        <v>66</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="C20" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
         <v>12</v>
       </c>
-      <c r="G18">
+      <c r="G20">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Altamirano Victorino Juventino - Estadisticos 20221.xlsx
+++ b/docentes/González Altamirano Victorino Juventino - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="77">
   <si>
     <t>Mat</t>
   </si>
@@ -79,34 +79,55 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>MAY</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
     <t>MEDINA</t>
   </si>
   <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>LEYVA</t>
   </si>
   <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>TELE</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>MAY</t>
-  </si>
-  <si>
-    <t>REYES</t>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>APONTE</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
   </si>
   <si>
     <t>CASTRO</t>
@@ -115,127 +136,118 @@
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>APONTE</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>ZEPACTLE</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>VIDERIQUE</t>
+  </si>
+  <si>
+    <t>TEQUILIQUIHUA</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>PALACIOS</t>
+  </si>
+  <si>
+    <t>CHIMALHUA</t>
   </si>
   <si>
     <t>VELASQUEZ</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
     <t>DELGADO</t>
   </si>
   <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>ZEPACTLE</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>VIDERIQUE</t>
+    <t>OYOLA</t>
+  </si>
+  <si>
+    <t>OJEDA</t>
   </si>
   <si>
     <t>MONTIEL</t>
   </si>
   <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
     <t>LUNA</t>
   </si>
   <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>CHIMALHUA</t>
-  </si>
-  <si>
-    <t>OYOLA</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
+    <t>ESTEPHANY SOPHIA</t>
+  </si>
+  <si>
+    <t>EVIAN ISSAIAS</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>GABRIELA AIMEE</t>
+  </si>
+  <si>
+    <t>BELEN</t>
+  </si>
+  <si>
+    <t>ESTEFANY VIANEY</t>
+  </si>
+  <si>
+    <t>MARIAM</t>
+  </si>
+  <si>
+    <t>OSMAR UZIEL</t>
+  </si>
+  <si>
+    <t>EMILIANO GERARDO</t>
   </si>
   <si>
     <t>VALERIA DANAY</t>
   </si>
   <si>
+    <t>EVELYN ROSALIA</t>
+  </si>
+  <si>
+    <t>SALMA AISHA</t>
+  </si>
+  <si>
     <t>ESTRELLA</t>
   </si>
   <si>
-    <t>JIMENA</t>
-  </si>
-  <si>
-    <t>LUZ YAMILET</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
-  </si>
-  <si>
     <t>DAMON</t>
   </si>
   <si>
-    <t>BETSABETH</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
-    <t>GABRIELA AIMEE</t>
-  </si>
-  <si>
-    <t>BELEN</t>
+    <t>IVON</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>ABIGAIL ANTONIA</t>
   </si>
   <si>
     <t>LESLY VIANEY</t>
   </si>
   <si>
+    <t>IVETTE NAOMI</t>
+  </si>
+  <si>
     <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>EMILIANO GERARDO</t>
-  </si>
-  <si>
-    <t>EVELYN ROSALIA</t>
-  </si>
-  <si>
-    <t>SALMA AISHA</t>
-  </si>
-  <si>
-    <t>IVON</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>ABIGAIL ANTONIA</t>
-  </si>
-  <si>
-    <t>IVETTE NAOMI</t>
   </si>
 </sst>
 </file>
@@ -711,7 +723,7 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -720,10 +732,10 @@
         <v>10</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G5">
-        <v>73.81</v>
+        <v>74.42</v>
       </c>
       <c r="H5">
         <v>7.2</v>
@@ -871,13 +883,13 @@
         <v>12</v>
       </c>
       <c r="C5">
+        <v>43</v>
+      </c>
+      <c r="D5">
+        <v>43</v>
+      </c>
+      <c r="E5">
         <v>42</v>
-      </c>
-      <c r="D5">
-        <v>42</v>
-      </c>
-      <c r="E5">
-        <v>41</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1034,7 +1046,7 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1043,10 +1055,10 @@
         <v>10</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G5">
-        <v>73.81</v>
+        <v>74.42</v>
       </c>
       <c r="H5">
         <v>7.2</v>
@@ -1085,7 +1097,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1117,16 +1129,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920216</v>
+        <v>22330051920362</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1140,22 +1152,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920067</v>
+        <v>22330051920215</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1163,16 +1175,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920068</v>
+        <v>22330051920084</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1186,22 +1198,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920069</v>
+        <v>22330051920131</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1209,22 +1221,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920084</v>
+        <v>22330051920136</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1232,22 +1244,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920337</v>
+        <v>22330051920141</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1255,22 +1267,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920121</v>
+        <v>22330051920142</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1278,22 +1290,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920131</v>
+        <v>22330051920160</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1301,22 +1313,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920136</v>
+        <v>22330051920382</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1324,91 +1336,91 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920141</v>
+        <v>22330051920205</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920155</v>
+        <v>22330051920216</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920386</v>
+        <v>22330051920222</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
         <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920205</v>
+        <v>22330051920062</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
         <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1416,22 +1428,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920222</v>
+        <v>22330051920067</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
         <v>49</v>
       </c>
       <c r="D15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1439,22 +1451,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920062</v>
+        <v>22330051920337</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
         <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1465,13 +1477,13 @@
         <v>22330051920119</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
         <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1488,13 +1500,13 @@
         <v>22330051920125</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1511,13 +1523,13 @@
         <v>22330051920130</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
         <v>52</v>
       </c>
       <c r="D19" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1531,16 +1543,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920269</v>
+        <v>22330051920155</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
         <v>53</v>
       </c>
       <c r="D20" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1549,6 +1561,52 @@
         <v>12</v>
       </c>
       <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>22330051920269</v>
+      </c>
+      <c r="B21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>22330051920386</v>
+      </c>
+      <c r="B22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Altamirano Victorino Juventino - Estadisticos 20221.xlsx
+++ b/docentes/González Altamirano Victorino Juventino - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="74">
   <si>
     <t>Mat</t>
   </si>
@@ -85,24 +85,27 @@
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>MAY</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
+    <t>TELE</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
   </si>
   <si>
     <t>COCOTLE</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
@@ -112,100 +115,94 @@
     <t>RAMOS</t>
   </si>
   <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>APONTE</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>PRADO</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>TEQUILIQUIHUA</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>PALACIOS</t>
+  </si>
+  <si>
+    <t>VELASQUEZ</t>
+  </si>
+  <si>
+    <t>DELGADO</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>APONTE</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>ZEPACTLE</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>VIDERIQUE</t>
-  </si>
-  <si>
-    <t>TEQUILIQUIHUA</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>CHIMALHUA</t>
-  </si>
-  <si>
-    <t>VELASQUEZ</t>
-  </si>
-  <si>
-    <t>DELGADO</t>
-  </si>
-  <si>
-    <t>OYOLA</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
     <t>VILLEGAS</t>
   </si>
   <si>
-    <t>LUNA</t>
-  </si>
-  <si>
     <t>ESTEPHANY SOPHIA</t>
   </si>
   <si>
     <t>EVIAN ISSAIAS</t>
   </si>
   <si>
+    <t>MICHELLE</t>
+  </si>
+  <si>
+    <t>DANIEL ELEAZAR</t>
+  </si>
+  <si>
     <t>JOSE MIGUEL</t>
   </si>
   <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
-    <t>GABRIELA AIMEE</t>
-  </si>
-  <si>
-    <t>BELEN</t>
-  </si>
-  <si>
-    <t>ESTEFANY VIANEY</t>
+    <t>ANETTE</t>
+  </si>
+  <si>
+    <t>BETSABETH</t>
+  </si>
+  <si>
+    <t>ESTEFANY CELESTE</t>
   </si>
   <si>
     <t>MARIAM</t>
@@ -214,6 +211,9 @@
     <t>OSMAR UZIEL</t>
   </si>
   <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
     <t>EMILIANO GERARDO</t>
   </si>
   <si>
@@ -223,31 +223,22 @@
     <t>EVELYN ROSALIA</t>
   </si>
   <si>
-    <t>SALMA AISHA</t>
-  </si>
-  <si>
     <t>ESTRELLA</t>
   </si>
   <si>
     <t>DAMON</t>
   </si>
   <si>
-    <t>IVON</t>
+    <t>TOBIAS</t>
   </si>
   <si>
     <t>MARIA FERNANDA</t>
   </si>
   <si>
-    <t>ABIGAIL ANTONIA</t>
-  </si>
-  <si>
-    <t>LESLY VIANEY</t>
+    <t>XIMENA</t>
   </si>
   <si>
     <t>IVETTE NAOMI</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
   </si>
 </sst>
 </file>
@@ -817,16 +808,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="H2">
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -840,16 +834,19 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>84.09</v>
+      </c>
+      <c r="H3">
+        <v>7.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -863,16 +860,19 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>76.73999999999999</v>
+      </c>
+      <c r="H4">
+        <v>7.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -886,16 +886,19 @@
         <v>43</v>
       </c>
       <c r="D5">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>74.42</v>
+      </c>
+      <c r="H5">
+        <v>7.2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -909,16 +912,19 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>64.70999999999999</v>
+      </c>
+      <c r="H6">
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -974,16 +980,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>82.5</v>
+        <v>80</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1009,7 +1015,7 @@
         <v>84.09</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1026,16 +1032,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>79.06999999999999</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1061,7 +1067,7 @@
         <v>74.42</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1078,16 +1084,16 @@
         <v>1</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F6">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G6">
-        <v>70.59</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="H6">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1103,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1135,10 +1141,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1158,10 +1164,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1175,22 +1181,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920084</v>
+        <v>22330051920224</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1198,22 +1204,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920131</v>
+        <v>22330051920064</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1221,22 +1227,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920136</v>
+        <v>22330051920084</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1244,22 +1250,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920141</v>
+        <v>22330051920098</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1267,22 +1273,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920142</v>
+        <v>22330051920121</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1290,22 +1296,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920160</v>
+        <v>22330051920126</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
         <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1313,16 +1319,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920382</v>
+        <v>22330051920160</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
         <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1336,62 +1342,62 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920205</v>
+        <v>22330051920382</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
         <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920216</v>
+        <v>22330051920386</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920222</v>
+        <v>22330051920205</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1405,22 +1411,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920062</v>
+        <v>22330051920216</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1428,22 +1434,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920067</v>
+        <v>22330051920222</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
         <v>49</v>
       </c>
       <c r="D15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1451,22 +1457,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920337</v>
+        <v>22330051920067</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
         <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1474,16 +1480,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920119</v>
+        <v>22330051920337</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C17" t="s">
         <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1497,16 +1503,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920125</v>
+        <v>22330051920124</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="D18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1520,16 +1526,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920130</v>
+        <v>22330051920125</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="D19" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1543,22 +1549,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920155</v>
+        <v>22330051920132</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="D20" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1572,10 +1578,10 @@
         <v>21</v>
       </c>
       <c r="C21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D21" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1584,29 +1590,6 @@
         <v>12</v>
       </c>
       <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>22330051920386</v>
-      </c>
-      <c r="B22" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" t="s">
-        <v>55</v>
-      </c>
-      <c r="D22" t="s">
-        <v>76</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G22">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Altamirano Victorino Juventino - Estadisticos 20221.xlsx
+++ b/docentes/González Altamirano Victorino Juventino - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="72">
   <si>
     <t>Mat</t>
   </si>
@@ -79,12 +79,12 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
     <t>SILVESTRE</t>
   </si>
   <si>
@@ -109,9 +109,6 @@
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
     <t>RAMOS</t>
   </si>
   <si>
@@ -130,12 +127,12 @@
     <t>FLORES</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>OLIVARES</t>
   </si>
   <si>
@@ -181,12 +178,12 @@
     <t>VILLEGAS</t>
   </si>
   <si>
-    <t>ESTEPHANY SOPHIA</t>
-  </si>
-  <si>
     <t>EVIAN ISSAIAS</t>
   </si>
   <si>
+    <t>VALERIA DANAY</t>
+  </si>
+  <si>
     <t>MICHELLE</t>
   </si>
   <si>
@@ -215,9 +212,6 @@
   </si>
   <si>
     <t>EMILIANO GERARDO</t>
-  </si>
-  <si>
-    <t>VALERIA DANAY</t>
   </si>
   <si>
     <t>EVELYN ROSALIA</t>
@@ -1103,7 +1097,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1135,16 +1129,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920362</v>
+        <v>22330051920215</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1158,16 +1152,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920215</v>
+        <v>22330051920216</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1187,10 +1181,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1210,10 +1204,10 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1233,10 +1227,10 @@
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1256,10 +1250,10 @@
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1279,10 +1273,10 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1302,10 +1296,10 @@
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1325,10 +1319,10 @@
         <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1345,13 +1339,13 @@
         <v>22330051920382</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1371,10 +1365,10 @@
         <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1394,10 +1388,10 @@
         <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1411,16 +1405,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920216</v>
+        <v>22330051920222</v>
       </c>
       <c r="B14" t="s">
         <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1434,7 +1428,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920222</v>
+        <v>22330051920067</v>
       </c>
       <c r="B15" t="s">
         <v>31</v>
@@ -1443,13 +1437,13 @@
         <v>49</v>
       </c>
       <c r="D15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1457,7 +1451,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920067</v>
+        <v>22330051920337</v>
       </c>
       <c r="B16" t="s">
         <v>32</v>
@@ -1466,13 +1460,13 @@
         <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1480,7 +1474,7 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920337</v>
+        <v>22330051920124</v>
       </c>
       <c r="B17" t="s">
         <v>33</v>
@@ -1489,13 +1483,13 @@
         <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1503,16 +1497,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920124</v>
+        <v>22330051920125</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="D18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1526,16 +1520,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920125</v>
+        <v>22330051920132</v>
       </c>
       <c r="B19" t="s">
         <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="D19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1549,47 +1543,24 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920132</v>
+        <v>22330051920269</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C20" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="D20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>22330051920269</v>
-      </c>
-      <c r="B21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" t="s">
-        <v>53</v>
-      </c>
-      <c r="D21" t="s">
-        <v>73</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Altamirano Victorino Juventino - Estadisticos 20221.xlsx
+++ b/docentes/González Altamirano Victorino Juventino - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="70">
   <si>
     <t>Mat</t>
   </si>
@@ -175,9 +175,6 @@
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
     <t>EVIAN ISSAIAS</t>
   </si>
   <si>
@@ -230,9 +227,6 @@
   </si>
   <si>
     <t>XIMENA</t>
-  </si>
-  <si>
-    <t>IVETTE NAOMI</t>
   </si>
 </sst>
 </file>
@@ -711,16 +705,16 @@
         <v>43</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>10</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G5">
-        <v>74.42</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="H5">
         <v>7.2</v>
@@ -737,16 +731,16 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>9</v>
       </c>
       <c r="F6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G6">
-        <v>70.59</v>
+        <v>73.53</v>
       </c>
       <c r="H6">
         <v>6.6</v>
@@ -880,16 +874,16 @@
         <v>43</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>10</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G5">
-        <v>74.42</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="H5">
         <v>7.2</v>
@@ -906,16 +900,16 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>11</v>
       </c>
       <c r="F6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G6">
-        <v>64.70999999999999</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="H6">
         <v>6.6</v>
@@ -1049,16 +1043,16 @@
         <v>43</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>10</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G5">
-        <v>74.42</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="H5">
         <v>7</v>
@@ -1075,16 +1069,16 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>11</v>
       </c>
       <c r="F6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G6">
-        <v>64.70999999999999</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="H6">
         <v>6.7</v>
@@ -1097,7 +1091,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1138,7 +1132,7 @@
         <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1161,7 +1155,7 @@
         <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1184,7 +1178,7 @@
         <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1207,7 +1201,7 @@
         <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1230,7 +1224,7 @@
         <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1253,7 +1247,7 @@
         <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1276,7 +1270,7 @@
         <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1299,7 +1293,7 @@
         <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1322,7 +1316,7 @@
         <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1345,7 +1339,7 @@
         <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1368,7 +1362,7 @@
         <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1391,7 +1385,7 @@
         <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1414,7 +1408,7 @@
         <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1437,7 +1431,7 @@
         <v>49</v>
       </c>
       <c r="D15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1460,7 +1454,7 @@
         <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1483,7 +1477,7 @@
         <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1506,7 +1500,7 @@
         <v>37</v>
       </c>
       <c r="D18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1529,7 +1523,7 @@
         <v>23</v>
       </c>
       <c r="D19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1538,29 +1532,6 @@
         <v>11</v>
       </c>
       <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>22330051920269</v>
-      </c>
-      <c r="B20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" t="s">
-        <v>71</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Altamirano Victorino Juventino - Estadisticos 20221.xlsx
+++ b/docentes/González Altamirano Victorino Juventino - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="73">
   <si>
     <t>Mat</t>
   </si>
@@ -79,30 +79,33 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>TELE</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>TELE</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
@@ -127,42 +130,45 @@
     <t>FLORES</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ESPARZA</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>PRADO</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>TEQUILIQUIHUA</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>PRADO</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>TEQUILIQUIHUA</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
     <t>PALACIOS</t>
   </si>
   <si>
@@ -175,40 +181,43 @@
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>VALERIA DANAY</t>
+  </si>
+  <si>
+    <t>ANGELES VALERIA</t>
+  </si>
+  <si>
+    <t>MICHELLE</t>
+  </si>
+  <si>
+    <t>DANIEL ELEAZAR</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>ANETTE</t>
+  </si>
+  <si>
+    <t>BETSABETH</t>
+  </si>
+  <si>
+    <t>ESTEFANY CELESTE</t>
+  </si>
+  <si>
+    <t>MARIAM</t>
+  </si>
+  <si>
+    <t>OSMAR UZIEL</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>EMILIANO GERARDO</t>
+  </si>
+  <si>
     <t>EVIAN ISSAIAS</t>
-  </si>
-  <si>
-    <t>VALERIA DANAY</t>
-  </si>
-  <si>
-    <t>MICHELLE</t>
-  </si>
-  <si>
-    <t>DANIEL ELEAZAR</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>ANETTE</t>
-  </si>
-  <si>
-    <t>BETSABETH</t>
-  </si>
-  <si>
-    <t>ESTEFANY CELESTE</t>
-  </si>
-  <si>
-    <t>MARIAM</t>
-  </si>
-  <si>
-    <t>OSMAR UZIEL</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>EMILIANO GERARDO</t>
   </si>
   <si>
     <t>EVELYN ROSALIA</t>
@@ -1091,7 +1100,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1123,16 +1132,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920215</v>
+        <v>22330051920216</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1146,16 +1155,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920216</v>
+        <v>22330051920218</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1175,10 +1184,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1198,10 +1207,10 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1221,10 +1230,10 @@
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1244,10 +1253,10 @@
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1267,10 +1276,10 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1290,10 +1299,10 @@
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1313,10 +1322,10 @@
         <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1333,13 +1342,13 @@
         <v>22330051920382</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1356,13 +1365,13 @@
         <v>22330051920386</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1379,13 +1388,13 @@
         <v>22330051920205</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1399,16 +1408,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920222</v>
+        <v>22330051920215</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1422,22 +1431,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920067</v>
+        <v>22330051920222</v>
       </c>
       <c r="B15" t="s">
         <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1445,22 +1454,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920337</v>
+        <v>22330051920067</v>
       </c>
       <c r="B16" t="s">
         <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1468,22 +1477,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920124</v>
+        <v>22330051920337</v>
       </c>
       <c r="B17" t="s">
         <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1491,16 +1500,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920125</v>
+        <v>22330051920124</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="D18" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1514,16 +1523,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920132</v>
+        <v>22330051920125</v>
       </c>
       <c r="B19" t="s">
         <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="D19" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1532,6 +1541,29 @@
         <v>11</v>
       </c>
       <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>22330051920132</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Altamirano Victorino Juventino - Estadisticos 20221.xlsx
+++ b/docentes/González Altamirano Victorino Juventino - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="75">
   <si>
     <t>Mat</t>
   </si>
@@ -79,6 +79,9 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
     <t>MEDINA</t>
   </si>
   <si>
@@ -179,6 +182,9 @@
   </si>
   <si>
     <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>ESTEPHANY SOPHIA</t>
   </si>
   <si>
     <t>VALERIA DANAY</t>
@@ -1100,7 +1106,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1132,16 +1138,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920216</v>
+        <v>22330051920362</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1155,7 +1161,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920218</v>
+        <v>22330051920216</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
@@ -1164,7 +1170,7 @@
         <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1178,7 +1184,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920224</v>
+        <v>22330051920218</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
@@ -1187,7 +1193,7 @@
         <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1201,7 +1207,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920064</v>
+        <v>22330051920224</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
@@ -1210,13 +1216,13 @@
         <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1224,7 +1230,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920084</v>
+        <v>22330051920064</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -1233,7 +1239,7 @@
         <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1247,22 +1253,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920098</v>
+        <v>22330051920084</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
         <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1270,16 +1276,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920121</v>
+        <v>22330051920098</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
         <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1293,7 +1299,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920126</v>
+        <v>22330051920121</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
@@ -1302,13 +1308,13 @@
         <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1316,7 +1322,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920160</v>
+        <v>22330051920126</v>
       </c>
       <c r="B10" t="s">
         <v>27</v>
@@ -1325,13 +1331,13 @@
         <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1339,7 +1345,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920382</v>
+        <v>22330051920160</v>
       </c>
       <c r="B11" t="s">
         <v>28</v>
@@ -1348,7 +1354,7 @@
         <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1362,7 +1368,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920386</v>
+        <v>22330051920382</v>
       </c>
       <c r="B12" t="s">
         <v>29</v>
@@ -1371,7 +1377,7 @@
         <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1385,7 +1391,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920205</v>
+        <v>22330051920386</v>
       </c>
       <c r="B13" t="s">
         <v>30</v>
@@ -1394,30 +1400,30 @@
         <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920215</v>
+        <v>22330051920205</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
         <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1431,16 +1437,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920222</v>
+        <v>22330051920215</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s">
         <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1454,7 +1460,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920067</v>
+        <v>22330051920222</v>
       </c>
       <c r="B16" t="s">
         <v>32</v>
@@ -1463,13 +1469,13 @@
         <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1477,7 +1483,7 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920337</v>
+        <v>22330051920067</v>
       </c>
       <c r="B17" t="s">
         <v>33</v>
@@ -1486,13 +1492,13 @@
         <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1500,7 +1506,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920124</v>
+        <v>22330051920337</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
@@ -1509,13 +1515,13 @@
         <v>53</v>
       </c>
       <c r="D18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1523,16 +1529,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920125</v>
+        <v>22330051920124</v>
       </c>
       <c r="B19" t="s">
         <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="D19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1546,16 +1552,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920132</v>
+        <v>22330051920125</v>
       </c>
       <c r="B20" t="s">
         <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D20" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1564,6 +1570,29 @@
         <v>11</v>
       </c>
       <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>22330051920132</v>
+      </c>
+      <c r="B21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" t="s">
+        <v>74</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Altamirano Victorino Juventino - Estadisticos 20221.xlsx
+++ b/docentes/González Altamirano Victorino Juventino - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="78">
   <si>
     <t>Mat</t>
   </si>
@@ -97,6 +97,9 @@
     <t>VELAZQUEZ</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>TELE</t>
   </si>
   <si>
@@ -151,6 +154,9 @@
     <t>PRADO</t>
   </si>
   <si>
+    <t>LUGO</t>
+  </si>
+  <si>
     <t>HUERTA</t>
   </si>
   <si>
@@ -203,6 +209,9 @@
   </si>
   <si>
     <t>ANETTE</t>
+  </si>
+  <si>
+    <t>ZAYRA</t>
   </si>
   <si>
     <t>BETSABETH</t>
@@ -1106,7 +1115,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1144,10 +1153,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1167,10 +1176,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1190,10 +1199,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1213,10 +1222,10 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1236,10 +1245,10 @@
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1259,10 +1268,10 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1282,10 +1291,10 @@
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1299,16 +1308,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920121</v>
+        <v>22330051920100</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1322,22 +1331,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920126</v>
+        <v>22330051920121</v>
       </c>
       <c r="B10" t="s">
         <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1345,22 +1354,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920160</v>
+        <v>22330051920126</v>
       </c>
       <c r="B11" t="s">
         <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1368,16 +1377,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920382</v>
+        <v>22330051920160</v>
       </c>
       <c r="B12" t="s">
         <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D12" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1391,16 +1400,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920386</v>
+        <v>22330051920382</v>
       </c>
       <c r="B13" t="s">
         <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1414,39 +1423,39 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920205</v>
+        <v>22330051920386</v>
       </c>
       <c r="B14" t="s">
         <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920215</v>
+        <v>22330051920205</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1460,16 +1469,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920222</v>
+        <v>22330051920215</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1483,22 +1492,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920067</v>
+        <v>22330051920222</v>
       </c>
       <c r="B17" t="s">
         <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D17" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1506,22 +1515,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920337</v>
+        <v>22330051920067</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1529,22 +1538,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920124</v>
+        <v>22330051920337</v>
       </c>
       <c r="B19" t="s">
         <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D19" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1552,16 +1561,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920125</v>
+        <v>22330051920124</v>
       </c>
       <c r="B20" t="s">
         <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="D20" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1575,16 +1584,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920132</v>
+        <v>22330051920125</v>
       </c>
       <c r="B21" t="s">
         <v>37</v>
       </c>
       <c r="C21" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="D21" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1593,6 +1602,29 @@
         <v>11</v>
       </c>
       <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>22330051920132</v>
+      </c>
+      <c r="B22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Altamirano Victorino Juventino - Estadisticos 20221.xlsx
+++ b/docentes/González Altamirano Victorino Juventino - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="51">
   <si>
     <t>Mat</t>
   </si>
@@ -91,51 +91,27 @@
     <t>SILVESTRE</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
+    <t>RODRIGUEZ</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>TELE</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
   </si>
   <si>
     <t>COCOTLE</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>APONTE</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
@@ -145,51 +121,24 @@
     <t>OLIVARES</t>
   </si>
   <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>PRADO</t>
+    <t>GARCIA</t>
   </si>
   <si>
     <t>LUGO</t>
   </si>
   <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
+    <t>ANGUIANO</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>PALACIOS</t>
   </si>
   <si>
     <t>TEQUILIQUIHUA</t>
   </si>
   <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>VELASQUEZ</t>
-  </si>
-  <si>
-    <t>DELGADO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>ESTEPHANY SOPHIA</t>
   </si>
   <si>
@@ -202,55 +151,25 @@
     <t>MICHELLE</t>
   </si>
   <si>
-    <t>DANIEL ELEAZAR</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>ANETTE</t>
+    <t>MELANIE SOFIA</t>
   </si>
   <si>
     <t>ZAYRA</t>
   </si>
   <si>
-    <t>BETSABETH</t>
-  </si>
-  <si>
-    <t>ESTEFANY CELESTE</t>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>EMILIANO GERARDO</t>
+  </si>
+  <si>
+    <t>EVIAN ISSAIAS</t>
+  </si>
+  <si>
+    <t>EVELYN ROSALIA</t>
   </si>
   <si>
     <t>MARIAM</t>
-  </si>
-  <si>
-    <t>OSMAR UZIEL</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>EMILIANO GERARDO</t>
-  </si>
-  <si>
-    <t>EVIAN ISSAIAS</t>
-  </si>
-  <si>
-    <t>EVELYN ROSALIA</t>
-  </si>
-  <si>
-    <t>ESTRELLA</t>
-  </si>
-  <si>
-    <t>DAMON</t>
-  </si>
-  <si>
-    <t>TOBIAS</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
   </si>
 </sst>
 </file>
@@ -992,16 +911,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G2">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1018,13 +937,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G3">
-        <v>84.09</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="H3">
         <v>7.4</v>
@@ -1044,13 +963,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G4">
-        <v>76.73999999999999</v>
+        <v>86.05</v>
       </c>
       <c r="H4">
         <v>7</v>
@@ -1070,16 +989,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G5">
-        <v>76.73999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1115,7 +1034,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1153,10 +1072,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1176,10 +1095,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1199,10 +1118,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1222,10 +1141,10 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1239,16 +1158,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920064</v>
+        <v>22330051920079</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1262,22 +1181,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920084</v>
+        <v>22330051920100</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1285,22 +1204,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920098</v>
+        <v>22330051920172</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1308,71 +1227,71 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920100</v>
+        <v>22330051920205</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920121</v>
+        <v>22330051920215</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920126</v>
+        <v>22330051920222</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1380,13 +1299,13 @@
         <v>22330051920160</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1395,236 +1314,6 @@
         <v>12</v>
       </c>
       <c r="G12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920382</v>
-      </c>
-      <c r="B13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" t="s">
-        <v>68</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920386</v>
-      </c>
-      <c r="B14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" t="s">
-        <v>69</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920205</v>
-      </c>
-      <c r="B15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" t="s">
-        <v>70</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920215</v>
-      </c>
-      <c r="B16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" t="s">
-        <v>71</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920222</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" t="s">
-        <v>72</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920067</v>
-      </c>
-      <c r="B18" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" t="s">
-        <v>54</v>
-      </c>
-      <c r="D18" t="s">
-        <v>73</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>9</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920337</v>
-      </c>
-      <c r="B19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" t="s">
-        <v>55</v>
-      </c>
-      <c r="D19" t="s">
-        <v>74</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>22330051920124</v>
-      </c>
-      <c r="B20" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20" t="s">
-        <v>75</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>11</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>22330051920125</v>
-      </c>
-      <c r="B21" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" t="s">
-        <v>39</v>
-      </c>
-      <c r="D21" t="s">
-        <v>76</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>11</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>22330051920132</v>
-      </c>
-      <c r="B22" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" t="s">
-        <v>24</v>
-      </c>
-      <c r="D22" t="s">
-        <v>77</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>11</v>
-      </c>
-      <c r="G22">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Altamirano Victorino Juventino - Estadisticos 20221.xlsx
+++ b/docentes/González Altamirano Victorino Juventino - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="46">
   <si>
     <t>Mat</t>
   </si>
@@ -79,37 +79,46 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>USCANGA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
     <t>ALFONSO</t>
   </si>
   <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
+    <t>JUAN</t>
+  </si>
+  <si>
+    <t>LUGO</t>
+  </si>
+  <si>
+    <t>TEQUILIQUIHUA</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>ANGUIANO</t>
   </si>
   <si>
     <t>SANCHEZ</t>
@@ -118,58 +127,34 @@
     <t>ESPARZA</t>
   </si>
   <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>LUGO</t>
-  </si>
-  <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>TEQUILIQUIHUA</t>
+    <t>LILIANA</t>
+  </si>
+  <si>
+    <t>EMILIANO DE JESUS</t>
+  </si>
+  <si>
+    <t>ZAYRA</t>
+  </si>
+  <si>
+    <t>MARIAM</t>
+  </si>
+  <si>
+    <t>MARIO</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
   </si>
   <si>
     <t>ESTEPHANY SOPHIA</t>
   </si>
   <si>
-    <t>VALERIA DANAY</t>
-  </si>
-  <si>
     <t>ANGELES VALERIA</t>
   </si>
   <si>
-    <t>MICHELLE</t>
-  </si>
-  <si>
     <t>MELANIE SOFIA</t>
-  </si>
-  <si>
-    <t>ZAYRA</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>EMILIANO GERARDO</t>
-  </si>
-  <si>
-    <t>EVIAN ISSAIAS</t>
-  </si>
-  <si>
-    <t>EVELYN ROSALIA</t>
-  </si>
-  <si>
-    <t>MARIAM</t>
   </si>
 </sst>
 </file>
@@ -1015,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G6">
-        <v>67.65000000000001</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H6">
         <v>6.7</v>
@@ -1034,7 +1019,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1066,16 +1051,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920362</v>
+        <v>22330051920213</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1089,16 +1074,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920216</v>
+        <v>22330051920365</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1112,22 +1097,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920218</v>
+        <v>22330051920100</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1135,22 +1120,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920224</v>
+        <v>22330051920160</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1158,22 +1143,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920079</v>
+        <v>22330051920296</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1181,22 +1166,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920100</v>
+        <v>22330051920172</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1204,39 +1189,39 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920172</v>
+        <v>22330051920362</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920205</v>
+        <v>22330051920218</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1250,70 +1235,24 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920215</v>
+        <v>22330051920079</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920222</v>
-      </c>
-      <c r="B11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920160</v>
-      </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Altamirano Victorino Juventino - Estadisticos 20221.xlsx
+++ b/docentes/González Altamirano Victorino Juventino - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="55">
   <si>
     <t>Mat</t>
   </si>
@@ -85,9 +85,18 @@
     <t>USCANGA</t>
   </si>
   <si>
+    <t>GAMBOA</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>MAY</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
     <t>COCOTLE</t>
   </si>
   <si>
@@ -109,9 +118,18 @@
     <t>JUAN</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>LUGO</t>
   </si>
   <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>VIDERIQUE</t>
+  </si>
+  <si>
     <t>TEQUILIQUIHUA</t>
   </si>
   <si>
@@ -136,7 +154,16 @@
     <t>EMILIANO DE JESUS</t>
   </si>
   <si>
+    <t>DIEGO ARMANDO</t>
+  </si>
+  <si>
     <t>ZAYRA</t>
+  </si>
+  <si>
+    <t>GABRIELA AIMEE</t>
+  </si>
+  <si>
+    <t>BELEN</t>
   </si>
   <si>
     <t>MARIAM</t>
@@ -1019,7 +1046,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1057,10 +1084,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1080,10 +1107,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1097,16 +1124,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920100</v>
+        <v>22330051920091</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1120,22 +1147,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920160</v>
+        <v>22330051920100</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1143,22 +1170,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920296</v>
+        <v>22330051920136</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1166,22 +1193,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920172</v>
+        <v>22330051920141</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1189,70 +1216,139 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920362</v>
+        <v>22330051920160</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920218</v>
+        <v>22330051920296</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920079</v>
+        <v>22330051920172</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920362</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920218</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>22330051920079</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
         <v>9</v>
       </c>
-      <c r="G10">
+      <c r="G13">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Altamirano Victorino Juventino - Estadisticos 20221.xlsx
+++ b/docentes/González Altamirano Victorino Juventino - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="52">
   <si>
     <t>Mat</t>
   </si>
@@ -85,103 +85,94 @@
     <t>USCANGA</t>
   </si>
   <si>
+    <t>MAY</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>GAMBOA</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MAY</t>
-  </si>
-  <si>
     <t>REYES</t>
   </si>
   <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>JUAN</t>
   </si>
   <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>TEQUILIQUIHUA</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>ANGUIANO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ESPARZA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>LUGO</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
     <t>VIDERIQUE</t>
   </si>
   <si>
-    <t>TEQUILIQUIHUA</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ESPARZA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>LILIANA</t>
   </si>
   <si>
     <t>EMILIANO DE JESUS</t>
   </si>
   <si>
+    <t>GABRIELA AIMEE</t>
+  </si>
+  <si>
+    <t>MARIAM</t>
+  </si>
+  <si>
+    <t>MARIO</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>ESTEPHANY SOPHIA</t>
+  </si>
+  <si>
+    <t>ANGELES VALERIA</t>
+  </si>
+  <si>
+    <t>MELANIE SOFIA</t>
+  </si>
+  <si>
     <t>DIEGO ARMANDO</t>
   </si>
   <si>
-    <t>ZAYRA</t>
-  </si>
-  <si>
-    <t>GABRIELA AIMEE</t>
-  </si>
-  <si>
     <t>BELEN</t>
-  </si>
-  <si>
-    <t>MARIAM</t>
-  </si>
-  <si>
-    <t>MARIO</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>ESTEPHANY SOPHIA</t>
-  </si>
-  <si>
-    <t>ANGELES VALERIA</t>
-  </si>
-  <si>
-    <t>MELANIE SOFIA</t>
   </si>
 </sst>
 </file>
@@ -1046,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1084,10 +1075,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1107,10 +1098,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1124,22 +1115,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920091</v>
+        <v>22330051920136</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1147,22 +1138,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920100</v>
+        <v>22330051920160</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1170,22 +1161,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920136</v>
+        <v>22330051920296</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1193,22 +1184,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920141</v>
+        <v>22330051920172</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1216,91 +1207,91 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920160</v>
+        <v>22330051920362</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920296</v>
+        <v>22330051920218</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920172</v>
+        <v>22330051920079</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920362</v>
+        <v>22330051920091</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1308,47 +1299,24 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920218</v>
+        <v>22330051920141</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920079</v>
-      </c>
-      <c r="B13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" t="s">
-        <v>54</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G13">
         <v>1</v>
       </c>
     </row>
